--- a/artfynd/A 46723-2025 artfynd.xlsx
+++ b/artfynd/A 46723-2025 artfynd.xlsx
@@ -675,64 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124774637</v>
+        <v>125571548</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kantzon mot gräsmark, Stortjärnen, Sikåsån, Hammerdal, Jmt</t>
+          <t>Gamla stigen, Öjån, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517933</v>
+        <v>518115</v>
       </c>
       <c r="R2" t="n">
-        <v>7054139</v>
+        <v>7054844</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,45 +776,46 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elisabeth Olsson Hedin</t>
+          <t>Joakim Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elisabeth Olsson Hedin</t>
+          <t>Joakim Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125571923</v>
+        <v>124774637</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,26 +829,30 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gamla stigen, Öjån, Hammerdal, Jmt</t>
+          <t>Kantzon mot gräsmark, Stortjärnen, Sikåsån, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518115</v>
+        <v>517933</v>
       </c>
       <c r="R3" t="n">
-        <v>7054844</v>
+        <v>7054139</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joakim Danielsson</t>
+          <t>Elisabeth Olsson Hedin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Danielsson</t>
+          <t>Elisabeth Olsson Hedin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125571886</v>
+        <v>125571818</v>
       </c>
       <c r="B4" t="n">
-        <v>57812</v>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +955,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -999,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,32 +1037,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125571818</v>
+        <v>125571923</v>
       </c>
       <c r="B5" t="n">
-        <v>57934</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1118,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,46 +1156,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125571609</v>
+        <v>125571886</v>
       </c>
       <c r="B6" t="n">
-        <v>98263</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1237,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1257,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125571548</v>
+        <v>125571609</v>
       </c>
       <c r="B7" t="n">
-        <v>98251</v>
+        <v>99036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,26 +1286,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 46723-2025 artfynd.xlsx
+++ b/artfynd/A 46723-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571548</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774637</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571886</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,8 +1422,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571609</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>